--- a/students-6.xlsx
+++ b/students-6.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="308">
   <si>
     <t>ZipGrade ID</t>
   </si>
@@ -34,6 +34,393 @@
     <t>Classes</t>
   </si>
   <si>
+    <t>ERIKA VANESSA</t>
+  </si>
+  <si>
+    <t>ARENAS BERMUDEZ</t>
+  </si>
+  <si>
+    <t>xF9VBga</t>
+  </si>
+  <si>
+    <t>Química 11-1</t>
+  </si>
+  <si>
+    <t>RICARDO ALEXIS</t>
+  </si>
+  <si>
+    <t>CASTRO MONTOYA</t>
+  </si>
+  <si>
+    <t>ysj9a9X</t>
+  </si>
+  <si>
+    <t>Química 10-2</t>
+  </si>
+  <si>
+    <t>CRISTIAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>COGUA AMORTEGUI</t>
+  </si>
+  <si>
+    <t>nad47WV</t>
+  </si>
+  <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
+    <t>BUSTOS JURADO</t>
+  </si>
+  <si>
+    <t>j8g9xjq</t>
+  </si>
+  <si>
+    <t>QUÍMICA 10-1</t>
+  </si>
+  <si>
+    <t>JUAN DAVID</t>
+  </si>
+  <si>
+    <t>OSORIO AGUIRRE</t>
+  </si>
+  <si>
+    <t>pR7dHVd</t>
+  </si>
+  <si>
+    <t>KAROL DANIELA</t>
+  </si>
+  <si>
+    <t>BELTRAN GARCIA</t>
+  </si>
+  <si>
+    <t>dys2CdZ</t>
+  </si>
+  <si>
+    <t>QUÍMICA 11-2</t>
+  </si>
+  <si>
+    <t>JUAN JOSE</t>
+  </si>
+  <si>
+    <t>CARDONA RIVERA</t>
+  </si>
+  <si>
+    <t>cH2swMM</t>
+  </si>
+  <si>
+    <t>Johan Sammir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ara Londoño </t>
+  </si>
+  <si>
+    <t>nj8n6ys</t>
+  </si>
+  <si>
+    <t>SEBASTIAN</t>
+  </si>
+  <si>
+    <t>ROJAS GUZMAN</t>
+  </si>
+  <si>
+    <t>JHmGvZC</t>
+  </si>
+  <si>
+    <t>CRISTIAN DAVID</t>
+  </si>
+  <si>
+    <t>LAVERDE ARANGO</t>
+  </si>
+  <si>
+    <t>WJ9L4F9</t>
+  </si>
+  <si>
+    <t>JUAN DIEGO</t>
+  </si>
+  <si>
+    <t>GALEANO CARRIAZO</t>
+  </si>
+  <si>
+    <t>dT6xfuR</t>
+  </si>
+  <si>
+    <t>ANDERSON STEVEN</t>
+  </si>
+  <si>
+    <t>GUERRA MORALES</t>
+  </si>
+  <si>
+    <t>Rtjmehj</t>
+  </si>
+  <si>
+    <t>ANA SOFIA</t>
+  </si>
+  <si>
+    <t>ARBOLEDA RAMIREZ</t>
+  </si>
+  <si>
+    <t>Avs5gkn</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>CARDONA DUQUE</t>
+  </si>
+  <si>
+    <t>WX7Wx8S</t>
+  </si>
+  <si>
+    <t>SAMUEL ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ABELLA ARROYO</t>
+  </si>
+  <si>
+    <t>Nyeqe4y</t>
+  </si>
+  <si>
+    <t>VERONICA</t>
+  </si>
+  <si>
+    <t>VANEGAS VASQUEZ</t>
+  </si>
+  <si>
+    <t>GrGLJUM</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIÁN</t>
+  </si>
+  <si>
+    <t>QUINTERO REYES</t>
+  </si>
+  <si>
+    <t>2iBWuQt</t>
+  </si>
+  <si>
+    <t>JULIETH VANESSA</t>
+  </si>
+  <si>
+    <t>CORTES BERMUDEZ</t>
+  </si>
+  <si>
+    <t>8u4e2ua</t>
+  </si>
+  <si>
+    <t>GABRIELA</t>
+  </si>
+  <si>
+    <t>PEDRAZA SILVA</t>
+  </si>
+  <si>
+    <t>4Q2eBJK</t>
+  </si>
+  <si>
+    <t>ISABELLA</t>
+  </si>
+  <si>
+    <t>PEREZ BEJARANO</t>
+  </si>
+  <si>
+    <t>EEvpj1A</t>
+  </si>
+  <si>
+    <t>DIEGO LEANDRO</t>
+  </si>
+  <si>
+    <t>GARCIA MONTEALEGRE</t>
+  </si>
+  <si>
+    <t>9BTD889</t>
+  </si>
+  <si>
+    <t>YULI MARIANA</t>
+  </si>
+  <si>
+    <t>LLANO VANEGAS</t>
+  </si>
+  <si>
+    <t>XF9cDMw</t>
+  </si>
+  <si>
+    <t>JUAN SEBASTIAN</t>
+  </si>
+  <si>
+    <t>CARVAJAL LOPEZ</t>
+  </si>
+  <si>
+    <t>abca2fw</t>
+  </si>
+  <si>
+    <t>MICHEL</t>
+  </si>
+  <si>
+    <t>HENAO CASTAÑO</t>
+  </si>
+  <si>
+    <t>RWjfHrC</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ ARBELAEZ</t>
+  </si>
+  <si>
+    <t>4cmTbiF</t>
+  </si>
+  <si>
+    <t>DAVID SANTIAGO</t>
+  </si>
+  <si>
+    <t>GARCIA LOPEZ</t>
+  </si>
+  <si>
+    <t>mKhm9dn</t>
+  </si>
+  <si>
+    <t>LICETH FERNANDA</t>
+  </si>
+  <si>
+    <t>MUÑOZ MENDEZ</t>
+  </si>
+  <si>
+    <t>VyaaUXm</t>
+  </si>
+  <si>
+    <t>ISABELA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ PEÑUELA</t>
+  </si>
+  <si>
+    <t>yiZGjL5</t>
+  </si>
+  <si>
+    <t>JOHAN EXTIVEN</t>
+  </si>
+  <si>
+    <t>NUÑEZ GARCIA</t>
+  </si>
+  <si>
+    <t>GuS4Uyj</t>
+  </si>
+  <si>
+    <t>JUAN MANUEL</t>
+  </si>
+  <si>
+    <t>QUINTERO DUQUE</t>
+  </si>
+  <si>
+    <t>8xcuv3d</t>
+  </si>
+  <si>
+    <t>JAIRO ANDRES</t>
+  </si>
+  <si>
+    <t>ZAPATA MUÑOZ</t>
+  </si>
+  <si>
+    <t>MKSN8Xu</t>
+  </si>
+  <si>
+    <t>JANIER ESTIBEN</t>
+  </si>
+  <si>
+    <t>ATEHORTUA VILLA</t>
+  </si>
+  <si>
+    <t>Za4QVtQ</t>
+  </si>
+  <si>
+    <t>MARYERLY</t>
+  </si>
+  <si>
+    <t>MARIN VILLEGAS</t>
+  </si>
+  <si>
+    <t>sGeTT1S</t>
+  </si>
+  <si>
+    <t>AURIANNYS ALEJANDRA</t>
+  </si>
+  <si>
+    <t>PRASCA MORENO</t>
+  </si>
+  <si>
+    <t>vqMGRQq</t>
+  </si>
+  <si>
+    <t>ANGYLYTH KATHERINE</t>
+  </si>
+  <si>
+    <t>ESCOBAR ARISTIZÁBAL</t>
+  </si>
+  <si>
+    <t>iTBDrQH</t>
+  </si>
+  <si>
+    <t>LEIDY SOFIA</t>
+  </si>
+  <si>
+    <t>FUENTES PATIÑO</t>
+  </si>
+  <si>
+    <t>ewj1fsw</t>
+  </si>
+  <si>
+    <t>JOSUE MATEO</t>
+  </si>
+  <si>
+    <t>VIDAL VILLEGAS</t>
+  </si>
+  <si>
+    <t>xNx5CnX</t>
+  </si>
+  <si>
+    <t>PABLO JOSÉ</t>
+  </si>
+  <si>
+    <t>MORALES PAZ</t>
+  </si>
+  <si>
+    <t>kZ2Zyug</t>
+  </si>
+  <si>
+    <t>CASTILLO MARIN</t>
+  </si>
+  <si>
+    <t>E9fYbCx</t>
+  </si>
+  <si>
+    <t>NIKOL DANIELA</t>
+  </si>
+  <si>
+    <t>NIÑO USME</t>
+  </si>
+  <si>
+    <t>cesmt3F</t>
+  </si>
+  <si>
+    <t>KAHORY ALEJANDRA</t>
+  </si>
+  <si>
+    <t>VILLAR CASTAÑO</t>
+  </si>
+  <si>
+    <t>T8hKUJQ</t>
+  </si>
+  <si>
+    <t>KAREN JULIETH</t>
+  </si>
+  <si>
+    <t>RIVERA PINZÓN</t>
+  </si>
+  <si>
+    <t>V4HEqVf</t>
+  </si>
+  <si>
     <t>MIGUEL ANTONIO</t>
   </si>
   <si>
@@ -43,7 +430,286 @@
     <t>8YB8QPf</t>
   </si>
   <si>
-    <t>Química 10-2</t>
+    <t>GERLY</t>
+  </si>
+  <si>
+    <t>YATE RIOS</t>
+  </si>
+  <si>
+    <t>W2xCMsE</t>
+  </si>
+  <si>
+    <t>DYLAN DAYAN</t>
+  </si>
+  <si>
+    <t>MOLINA RIVERA</t>
+  </si>
+  <si>
+    <t>26tPF2X</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>MARIN OLAYA</t>
+  </si>
+  <si>
+    <t>Kpm7Cie</t>
+  </si>
+  <si>
+    <t>FRAN KEINER</t>
+  </si>
+  <si>
+    <t>CALDERON ACEVEDO</t>
+  </si>
+  <si>
+    <t>2GsDUVD</t>
+  </si>
+  <si>
+    <t>JORGE ANDRES</t>
+  </si>
+  <si>
+    <t>DIAZ BORRERO</t>
+  </si>
+  <si>
+    <t>PQX1a61</t>
+  </si>
+  <si>
+    <t>JESSICA ALEJANDRA</t>
+  </si>
+  <si>
+    <t>VASQUEZ GONZÁLES</t>
+  </si>
+  <si>
+    <t>QwxXXrq</t>
+  </si>
+  <si>
+    <t>CATHERIN</t>
+  </si>
+  <si>
+    <t>FLOREZ NIÑO</t>
+  </si>
+  <si>
+    <t>jjHUJ1E</t>
+  </si>
+  <si>
+    <t>GARATEJO RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>1WM9uHQ</t>
+  </si>
+  <si>
+    <t>WILMER MATEO</t>
+  </si>
+  <si>
+    <t>CALDERON PALOMO</t>
+  </si>
+  <si>
+    <t>WNZ37rb</t>
+  </si>
+  <si>
+    <t>ASLY VALERIA</t>
+  </si>
+  <si>
+    <t>MORENO CARDONA</t>
+  </si>
+  <si>
+    <t>S6V3FKE</t>
+  </si>
+  <si>
+    <t>ANDRES CAMILO</t>
+  </si>
+  <si>
+    <t>ROJAS ESCOBAR</t>
+  </si>
+  <si>
+    <t>Q8vYisE</t>
+  </si>
+  <si>
+    <t>CARDONA ARIAS</t>
+  </si>
+  <si>
+    <t>dLNfqVH</t>
+  </si>
+  <si>
+    <t>JUAN ESTEBAN</t>
+  </si>
+  <si>
+    <t>GARCIA CASTELLANOS</t>
+  </si>
+  <si>
+    <t>9HKmVtR</t>
+  </si>
+  <si>
+    <t>JULIANA</t>
+  </si>
+  <si>
+    <t>MONTOYA CARDONA</t>
+  </si>
+  <si>
+    <t>xKxq8j9</t>
+  </si>
+  <si>
+    <t>LAURA SOFIA</t>
+  </si>
+  <si>
+    <t>VILLAQUIRAN MARIN</t>
+  </si>
+  <si>
+    <t>wruXV8X</t>
+  </si>
+  <si>
+    <t>MONTERO RIVERA</t>
+  </si>
+  <si>
+    <t>wQsDHgX</t>
+  </si>
+  <si>
+    <t>ANA SHARYD</t>
+  </si>
+  <si>
+    <t>RAMIREZ CASTILLO</t>
+  </si>
+  <si>
+    <t>KnX714i</t>
+  </si>
+  <si>
+    <t>CRISTYN DAYANA</t>
+  </si>
+  <si>
+    <t>BALLESTEROS SANCHEZ</t>
+  </si>
+  <si>
+    <t>8nvXkmQ</t>
+  </si>
+  <si>
+    <t>GOMEZ CORZO</t>
+  </si>
+  <si>
+    <t>dAasYFJ</t>
+  </si>
+  <si>
+    <t>ALEXANDER</t>
+  </si>
+  <si>
+    <t>M3Mp3EA</t>
+  </si>
+  <si>
+    <t>MARIA PAULA</t>
+  </si>
+  <si>
+    <t>MOLINA LOPEZ</t>
+  </si>
+  <si>
+    <t>59KvAW6</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>OSORNO MARIA</t>
+  </si>
+  <si>
+    <t>hqinkeV</t>
+  </si>
+  <si>
+    <t>ELIZABETH</t>
+  </si>
+  <si>
+    <t>SANTAMARIA BERTHEL</t>
+  </si>
+  <si>
+    <t>73FRfFH</t>
+  </si>
+  <si>
+    <t>JUAN CAMILO</t>
+  </si>
+  <si>
+    <t>GOMEZ PEREZ</t>
+  </si>
+  <si>
+    <t>NH1iDaF</t>
+  </si>
+  <si>
+    <t>YIMMI SNEIDER</t>
+  </si>
+  <si>
+    <t>ACEVEDO CAMARGO</t>
+  </si>
+  <si>
+    <t>ARTFjmS</t>
+  </si>
+  <si>
+    <t>ESTEFANIA</t>
+  </si>
+  <si>
+    <t>BEDOYA ROJAS</t>
+  </si>
+  <si>
+    <t>XLWSCn8</t>
+  </si>
+  <si>
+    <t>BRILLID ALEXANDRA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ MURCIA</t>
+  </si>
+  <si>
+    <t>PBg6Qq4</t>
+  </si>
+  <si>
+    <t>BRANDON ADONAIS</t>
+  </si>
+  <si>
+    <t>HERNANDEZ ESCOBAR</t>
+  </si>
+  <si>
+    <t>JaNtxUx</t>
+  </si>
+  <si>
+    <t>BRIGITH NATALIA</t>
+  </si>
+  <si>
+    <t>LOZADA ROPERO</t>
+  </si>
+  <si>
+    <t>3eHg5pu</t>
+  </si>
+  <si>
+    <t>MARIANA</t>
+  </si>
+  <si>
+    <t>BEJARANO OSTOS</t>
+  </si>
+  <si>
+    <t>L8v7VLH</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>OSPINA CARDONA</t>
+  </si>
+  <si>
+    <t>8HFpBxH</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>MORENO ESCOBAR</t>
+  </si>
+  <si>
+    <t>DqQUdxq</t>
+  </si>
+  <si>
+    <t>LAURA DANIELA</t>
+  </si>
+  <si>
+    <t>VARGAS OSORIO</t>
+  </si>
+  <si>
+    <t>X9rVuTf</t>
   </si>
   <si>
     <t>HEIDY TATIANA</t>
@@ -55,34 +721,10 @@
     <t>EsWqjv1</t>
   </si>
   <si>
-    <t>KAROL DANIELA</t>
-  </si>
-  <si>
-    <t>BELTRAN GARCIA</t>
-  </si>
-  <si>
-    <t>dys2CdZ</t>
-  </si>
-  <si>
-    <t>QUÍMICA 11-2</t>
-  </si>
-  <si>
-    <t>LEIDY SOFIA</t>
-  </si>
-  <si>
-    <t>FUENTES PATIÑO</t>
-  </si>
-  <si>
-    <t>ewj1fsw</t>
-  </si>
-  <si>
-    <t>LICETH FERNANDA</t>
-  </si>
-  <si>
-    <t>MUÑOZ MENDEZ</t>
-  </si>
-  <si>
-    <t>VyaaUXm</t>
+    <t>CASTAÑO USME</t>
+  </si>
+  <si>
+    <t>DJG5sdH</t>
   </si>
   <si>
     <t>CESAR JOEL</t>
@@ -94,118 +736,121 @@
     <t>2Vq4VRg</t>
   </si>
   <si>
-    <t>QUÍMICA 10-1</t>
-  </si>
-  <si>
-    <t>YIMMI SNEIDER</t>
-  </si>
-  <si>
-    <t>ACEVEDO CAMARGO</t>
-  </si>
-  <si>
-    <t>ARTFjmS</t>
-  </si>
-  <si>
-    <t>KAREN JULIETH</t>
-  </si>
-  <si>
-    <t>RIVERA PINZÓN</t>
-  </si>
-  <si>
-    <t>V4HEqVf</t>
-  </si>
-  <si>
-    <t>MARIANA</t>
-  </si>
-  <si>
     <t>SUSUNAGA CARDONA</t>
   </si>
   <si>
     <t>pj4wLxp</t>
   </si>
   <si>
-    <t>ANDERSON STEVEN</t>
-  </si>
-  <si>
-    <t>GUERRA MORALES</t>
-  </si>
-  <si>
-    <t>Rtjmehj</t>
-  </si>
-  <si>
-    <t>GERLY</t>
-  </si>
-  <si>
-    <t>YATE RIOS</t>
-  </si>
-  <si>
-    <t>W2xCMsE</t>
-  </si>
-  <si>
-    <t>ISABELLA</t>
-  </si>
-  <si>
-    <t>PEREZ BEJARANO</t>
-  </si>
-  <si>
-    <t>EEvpj1A</t>
-  </si>
-  <si>
-    <t>ELIZABETH</t>
-  </si>
-  <si>
-    <t>SANTAMARIA BERTHEL</t>
-  </si>
-  <si>
-    <t>73FRfFH</t>
-  </si>
-  <si>
-    <t>JAIRO ANDRES</t>
-  </si>
-  <si>
-    <t>ZAPATA MUÑOZ</t>
-  </si>
-  <si>
-    <t>MKSN8Xu</t>
-  </si>
-  <si>
-    <t>CATHERIN</t>
-  </si>
-  <si>
-    <t>FLOREZ NIÑO</t>
-  </si>
-  <si>
-    <t>jjHUJ1E</t>
-  </si>
-  <si>
-    <t>JUAN JOSE</t>
-  </si>
-  <si>
-    <t>GARATEJO RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>1WM9uHQ</t>
-  </si>
-  <si>
-    <t>ERIKA VANESSA</t>
-  </si>
-  <si>
-    <t>ARENAS BERMUDEZ</t>
-  </si>
-  <si>
-    <t>xF9VBga</t>
-  </si>
-  <si>
-    <t>Química 11-1</t>
-  </si>
-  <si>
-    <t>JULIANA</t>
-  </si>
-  <si>
-    <t>GOMEZ CORZO</t>
-  </si>
-  <si>
-    <t>dAasYFJ</t>
+    <t>OSPINA JARAMILLO</t>
+  </si>
+  <si>
+    <t>TYtq2bC</t>
+  </si>
+  <si>
+    <t>KARINA</t>
+  </si>
+  <si>
+    <t>TOVAR RIOS</t>
+  </si>
+  <si>
+    <t>RM6ThYM</t>
+  </si>
+  <si>
+    <t>LAURA</t>
+  </si>
+  <si>
+    <t>GIRALDO QUICENO</t>
+  </si>
+  <si>
+    <t>pMxWcuS</t>
+  </si>
+  <si>
+    <t>MARIA CAMILA</t>
+  </si>
+  <si>
+    <t>ALZATE MORENO</t>
+  </si>
+  <si>
+    <t>1B6fRG5</t>
+  </si>
+  <si>
+    <t>JHOJAN CAMILO</t>
+  </si>
+  <si>
+    <t>CEBALLOS GALLEGO</t>
+  </si>
+  <si>
+    <t>D5XKcpj</t>
+  </si>
+  <si>
+    <t>YEFFERSON STEVEN</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ NARANJO</t>
+  </si>
+  <si>
+    <t>mt3UCwA</t>
+  </si>
+  <si>
+    <t>OSCAR EDUARDO</t>
+  </si>
+  <si>
+    <t>CASTAÑO CARRANZA</t>
+  </si>
+  <si>
+    <t>QTQ2qRM</t>
+  </si>
+  <si>
+    <t>DE LOS RIOS MONTOYA</t>
+  </si>
+  <si>
+    <t>N6bgiAE</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>DIAZ JORGE</t>
+  </si>
+  <si>
+    <t>HLY71Nr</t>
+  </si>
+  <si>
+    <t>RINCON OSORIO</t>
+  </si>
+  <si>
+    <t>8rCm7EB</t>
+  </si>
+  <si>
+    <t>BELTRAN MONTOYA</t>
+  </si>
+  <si>
+    <t>9ANLG2P</t>
+  </si>
+  <si>
+    <t>YICEL ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ACEVEDO PARRA</t>
+  </si>
+  <si>
+    <t>FeEPd3h</t>
+  </si>
+  <si>
+    <t>CASTAÑO BASTIDAS</t>
+  </si>
+  <si>
+    <t>CsPEirw</t>
+  </si>
+  <si>
+    <t>LISET MARIANA</t>
+  </si>
+  <si>
+    <t>LAZO TANGARIFE</t>
+  </si>
+  <si>
+    <t>fTcMpgt</t>
   </si>
   <si>
     <t>JOSÉ ANGEL</t>
@@ -217,76 +862,31 @@
     <t>AdCfinu</t>
   </si>
   <si>
-    <t>ASLY VALERIA</t>
-  </si>
-  <si>
-    <t>MORENO CARDONA</t>
-  </si>
-  <si>
-    <t>S6V3FKE</t>
-  </si>
-  <si>
-    <t>JUAN CAMILO</t>
-  </si>
-  <si>
-    <t>GOMEZ PEREZ</t>
-  </si>
-  <si>
-    <t>NH1iDaF</t>
-  </si>
-  <si>
-    <t>AURIANNYS ALEJANDRA</t>
-  </si>
-  <si>
-    <t>PRASCA MORENO</t>
-  </si>
-  <si>
-    <t>vqMGRQq</t>
-  </si>
-  <si>
-    <t>MICHEL</t>
-  </si>
-  <si>
-    <t>HENAO CASTAÑO</t>
-  </si>
-  <si>
-    <t>RWjfHrC</t>
-  </si>
-  <si>
-    <t>BRIGITH NATALIA</t>
-  </si>
-  <si>
-    <t>LOZADA ROPERO</t>
-  </si>
-  <si>
-    <t>3eHg5pu</t>
-  </si>
-  <si>
-    <t>JUAN MANUEL</t>
-  </si>
-  <si>
-    <t>MONTERO RIVERA</t>
-  </si>
-  <si>
-    <t>wQsDHgX</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>BUSTOS JURADO</t>
-  </si>
-  <si>
-    <t>j8g9xjq</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>DIAZ JORGE</t>
-  </si>
-  <si>
-    <t>HLY71Nr</t>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>BUSTOS GUEVARA</t>
+  </si>
+  <si>
+    <t>DF2pFmx</t>
+  </si>
+  <si>
+    <t>YISETH VANESSA</t>
+  </si>
+  <si>
+    <t>ESPINOSA ARBOLEDA</t>
+  </si>
+  <si>
+    <t>F4rp2H3</t>
+  </si>
+  <si>
+    <t>ALEXX</t>
+  </si>
+  <si>
+    <t>REYES MENDOZA</t>
+  </si>
+  <si>
+    <t>JCEgyUr</t>
   </si>
   <si>
     <t>YEIMI KATHERINE</t>
@@ -298,127 +898,22 @@
     <t>X7VgdJg</t>
   </si>
   <si>
-    <t>ANGYLYTH KATHERINE</t>
-  </si>
-  <si>
-    <t>ESCOBAR ARISTIZÁBAL</t>
-  </si>
-  <si>
-    <t>iTBDrQH</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>CARDONA DUQUE</t>
-  </si>
-  <si>
-    <t>WX7Wx8S</t>
-  </si>
-  <si>
-    <t>CRISTYN DAYANA</t>
-  </si>
-  <si>
-    <t>BALLESTEROS SANCHEZ</t>
-  </si>
-  <si>
-    <t>8nvXkmQ</t>
-  </si>
-  <si>
-    <t>RICARDO ALEXIS</t>
-  </si>
-  <si>
-    <t>CASTRO MONTOYA</t>
-  </si>
-  <si>
-    <t>ysj9a9X</t>
-  </si>
-  <si>
-    <t>QUINTERO DUQUE</t>
-  </si>
-  <si>
-    <t>8xcuv3d</t>
-  </si>
-  <si>
-    <t>MARIA PAULA</t>
-  </si>
-  <si>
-    <t>MOLINA LOPEZ</t>
-  </si>
-  <si>
-    <t>59KvAW6</t>
-  </si>
-  <si>
-    <t>ANDRES CAMILO</t>
-  </si>
-  <si>
-    <t>ROJAS ESCOBAR</t>
-  </si>
-  <si>
-    <t>Q8vYisE</t>
-  </si>
-  <si>
-    <t>MARYERLY</t>
-  </si>
-  <si>
-    <t>MARIN VILLEGAS</t>
-  </si>
-  <si>
-    <t>sGeTT1S</t>
-  </si>
-  <si>
-    <t>DYLAN DAYAN</t>
-  </si>
-  <si>
-    <t>MOLINA RIVERA</t>
-  </si>
-  <si>
-    <t>26tPF2X</t>
-  </si>
-  <si>
-    <t>YEFFERSON STEVEN</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ NARANJO</t>
-  </si>
-  <si>
-    <t>mt3UCwA</t>
-  </si>
-  <si>
-    <t>YICEL ALEJANDRA</t>
-  </si>
-  <si>
-    <t>ACEVEDO PARRA</t>
-  </si>
-  <si>
-    <t>FeEPd3h</t>
-  </si>
-  <si>
-    <t>SEBASTIAN</t>
-  </si>
-  <si>
-    <t>DE LOS RIOS MONTOYA</t>
-  </si>
-  <si>
-    <t>N6bgiAE</t>
-  </si>
-  <si>
-    <t>LAURA SOFIA</t>
-  </si>
-  <si>
-    <t>CASTAÑO USME</t>
-  </si>
-  <si>
-    <t>DJG5sdH</t>
-  </si>
-  <si>
-    <t>ANA SOFIA</t>
-  </si>
-  <si>
-    <t>ARBOLEDA RAMIREZ</t>
-  </si>
-  <si>
-    <t>Avs5gkn</t>
+    <t>JANNER DAVID</t>
+  </si>
+  <si>
+    <t>CORTEZ BERMUDEZ</t>
+  </si>
+  <si>
+    <t>3UKkPFR</t>
+  </si>
+  <si>
+    <t>BRAHYAN STEVEN</t>
+  </si>
+  <si>
+    <t>HENAO DUQUE</t>
+  </si>
+  <si>
+    <t>5T2R4eN</t>
   </si>
   <si>
     <t>STEFANY</t>
@@ -430,318 +925,12 @@
     <t>d7twyrQ</t>
   </si>
   <si>
-    <t>DAVID SANTIAGO</t>
-  </si>
-  <si>
-    <t>GARCIA LOPEZ</t>
-  </si>
-  <si>
-    <t>mKhm9dn</t>
-  </si>
-  <si>
-    <t>JUAN DAVID</t>
-  </si>
-  <si>
-    <t>OSORIO AGUIRRE</t>
-  </si>
-  <si>
-    <t>pR7dHVd</t>
-  </si>
-  <si>
-    <t>PABLO JOSÉ</t>
-  </si>
-  <si>
-    <t>MORALES PAZ</t>
-  </si>
-  <si>
-    <t>kZ2Zyug</t>
-  </si>
-  <si>
-    <t>ESTEFANIA</t>
-  </si>
-  <si>
-    <t>BEDOYA ROJAS</t>
-  </si>
-  <si>
-    <t>XLWSCn8</t>
-  </si>
-  <si>
-    <t>LAURA</t>
-  </si>
-  <si>
-    <t>GIRALDO QUICENO</t>
-  </si>
-  <si>
-    <t>pMxWcuS</t>
-  </si>
-  <si>
-    <t>CARDONA RIVERA</t>
-  </si>
-  <si>
-    <t>cH2swMM</t>
-  </si>
-  <si>
-    <t>KARINA</t>
-  </si>
-  <si>
-    <t>TOVAR RIOS</t>
-  </si>
-  <si>
-    <t>RM6ThYM</t>
-  </si>
-  <si>
-    <t>CASTILLO MARIN</t>
-  </si>
-  <si>
-    <t>E9fYbCx</t>
-  </si>
-  <si>
-    <t>MARIA CAMILA</t>
-  </si>
-  <si>
-    <t>ALZATE MORENO</t>
-  </si>
-  <si>
-    <t>1B6fRG5</t>
-  </si>
-  <si>
-    <t>JORGE ANDRES</t>
-  </si>
-  <si>
-    <t>DIAZ BORRERO</t>
-  </si>
-  <si>
-    <t>PQX1a61</t>
-  </si>
-  <si>
-    <t>YISETH VANESSA</t>
-  </si>
-  <si>
-    <t>ESPINOSA ARBOLEDA</t>
-  </si>
-  <si>
-    <t>F4rp2H3</t>
-  </si>
-  <si>
-    <t>JOSUE MATEO</t>
-  </si>
-  <si>
-    <t>VIDAL VILLEGAS</t>
-  </si>
-  <si>
-    <t>xNx5CnX</t>
-  </si>
-  <si>
-    <t>JHOJAN CAMILO</t>
-  </si>
-  <si>
-    <t>CEBALLOS GALLEGO</t>
-  </si>
-  <si>
-    <t>D5XKcpj</t>
-  </si>
-  <si>
-    <t>BEJARANO OSTOS</t>
-  </si>
-  <si>
-    <t>L8v7VLH</t>
-  </si>
-  <si>
-    <t>DIEGO LEANDRO</t>
-  </si>
-  <si>
-    <t>GARCIA MONTEALEGRE</t>
-  </si>
-  <si>
-    <t>9BTD889</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIÁN</t>
-  </si>
-  <si>
-    <t>QUINTERO REYES</t>
-  </si>
-  <si>
-    <t>2iBWuQt</t>
-  </si>
-  <si>
-    <t>NIKOL DANIELA</t>
-  </si>
-  <si>
-    <t>NIÑO USME</t>
-  </si>
-  <si>
-    <t>cesmt3F</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>MARIN OLAYA</t>
-  </si>
-  <si>
-    <t>Kpm7Cie</t>
-  </si>
-  <si>
-    <t>CRISTIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>COGUA AMORTEGUI</t>
-  </si>
-  <si>
-    <t>nad47WV</t>
-  </si>
-  <si>
-    <t>JUAN SEBASTIAN</t>
-  </si>
-  <si>
-    <t>CARVAJAL LOPEZ</t>
-  </si>
-  <si>
-    <t>abca2fw</t>
-  </si>
-  <si>
-    <t>JESSICA ALEJANDRA</t>
-  </si>
-  <si>
-    <t>VASQUEZ GONZÁLES</t>
-  </si>
-  <si>
-    <t>QwxXXrq</t>
-  </si>
-  <si>
-    <t>RINCON OSORIO</t>
-  </si>
-  <si>
-    <t>8rCm7EB</t>
-  </si>
-  <si>
-    <t>GABRIEL</t>
-  </si>
-  <si>
-    <t>OSPINA CARDONA</t>
-  </si>
-  <si>
-    <t>8HFpBxH</t>
-  </si>
-  <si>
-    <t>JULIETH VANESSA</t>
-  </si>
-  <si>
-    <t>CORTES BERMUDEZ</t>
-  </si>
-  <si>
-    <t>8u4e2ua</t>
-  </si>
-  <si>
-    <t>YULI MARIANA</t>
-  </si>
-  <si>
-    <t>LLANO VANEGAS</t>
-  </si>
-  <si>
-    <t>XF9cDMw</t>
-  </si>
-  <si>
-    <t>MONTOYA CARDONA</t>
-  </si>
-  <si>
-    <t>xKxq8j9</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>LOPEZ GIRALDO</t>
   </si>
   <si>
     <t>VneQNW5</t>
   </si>
   <si>
-    <t>LAURA DANIELA</t>
-  </si>
-  <si>
-    <t>VARGAS OSORIO</t>
-  </si>
-  <si>
-    <t>X9rVuTf</t>
-  </si>
-  <si>
-    <t>VILLAQUIRAN MARIN</t>
-  </si>
-  <si>
-    <t>wruXV8X</t>
-  </si>
-  <si>
-    <t>OSCAR EDUARDO</t>
-  </si>
-  <si>
-    <t>CASTAÑO CARRANZA</t>
-  </si>
-  <si>
-    <t>QTQ2qRM</t>
-  </si>
-  <si>
-    <t>BRANDON ADONAIS</t>
-  </si>
-  <si>
-    <t>HERNANDEZ ESCOBAR</t>
-  </si>
-  <si>
-    <t>JaNtxUx</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>OSORNO MARIA</t>
-  </si>
-  <si>
-    <t>hqinkeV</t>
-  </si>
-  <si>
-    <t>CRISTIAN DAVID</t>
-  </si>
-  <si>
-    <t>LAVERDE ARANGO</t>
-  </si>
-  <si>
-    <t>WJ9L4F9</t>
-  </si>
-  <si>
-    <t>JOHAN EXTIVEN</t>
-  </si>
-  <si>
-    <t>NUÑEZ GARCIA</t>
-  </si>
-  <si>
-    <t>GuS4Uyj</t>
-  </si>
-  <si>
-    <t>BRILLID ALEXANDRA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ MURCIA</t>
-  </si>
-  <si>
-    <t>PBg6Qq4</t>
-  </si>
-  <si>
-    <t>LISET MARIANA</t>
-  </si>
-  <si>
-    <t>LAZO TANGARIFE</t>
-  </si>
-  <si>
-    <t>fTcMpgt</t>
-  </si>
-  <si>
-    <t>HERNANDEZ ARBELAEZ</t>
-  </si>
-  <si>
-    <t>4cmTbiF</t>
-  </si>
-  <si>
     <t>JESUS MAURICIO</t>
   </si>
   <si>
@@ -749,186 +938,6 @@
   </si>
   <si>
     <t>x1uSNx3</t>
-  </si>
-  <si>
-    <t>ISABELA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ PEÑUELA</t>
-  </si>
-  <si>
-    <t>yiZGjL5</t>
-  </si>
-  <si>
-    <t>FRAN KEINER</t>
-  </si>
-  <si>
-    <t>CALDERON ACEVEDO</t>
-  </si>
-  <si>
-    <t>2GsDUVD</t>
-  </si>
-  <si>
-    <t>BELTRAN MONTOYA</t>
-  </si>
-  <si>
-    <t>9ANLG2P</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>BUSTOS GUEVARA</t>
-  </si>
-  <si>
-    <t>DF2pFmx</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>M3Mp3EA</t>
-  </si>
-  <si>
-    <t>SAMUEL ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ABELLA ARROYO</t>
-  </si>
-  <si>
-    <t>Nyeqe4y</t>
-  </si>
-  <si>
-    <t>JANIER ESTIBEN</t>
-  </si>
-  <si>
-    <t>ATEHORTUA VILLA</t>
-  </si>
-  <si>
-    <t>Za4QVtQ</t>
-  </si>
-  <si>
-    <t>JUAN DIEGO</t>
-  </si>
-  <si>
-    <t>GALEANO CARRIAZO</t>
-  </si>
-  <si>
-    <t>dT6xfuR</t>
-  </si>
-  <si>
-    <t>CARDONA ARIAS</t>
-  </si>
-  <si>
-    <t>dLNfqVH</t>
-  </si>
-  <si>
-    <t>ALEXX</t>
-  </si>
-  <si>
-    <t>REYES MENDOZA</t>
-  </si>
-  <si>
-    <t>JCEgyUr</t>
-  </si>
-  <si>
-    <t>JANNER DAVID</t>
-  </si>
-  <si>
-    <t>CORTEZ BERMUDEZ</t>
-  </si>
-  <si>
-    <t>3UKkPFR</t>
-  </si>
-  <si>
-    <t>OSPINA JARAMILLO</t>
-  </si>
-  <si>
-    <t>TYtq2bC</t>
-  </si>
-  <si>
-    <t>BRAHYAN STEVEN</t>
-  </si>
-  <si>
-    <t>HENAO DUQUE</t>
-  </si>
-  <si>
-    <t>5T2R4eN</t>
-  </si>
-  <si>
-    <t>GABRIELA</t>
-  </si>
-  <si>
-    <t>PEDRAZA SILVA</t>
-  </si>
-  <si>
-    <t>4Q2eBJK</t>
-  </si>
-  <si>
-    <t>CASTAÑO BASTIDAS</t>
-  </si>
-  <si>
-    <t>CsPEirw</t>
-  </si>
-  <si>
-    <t>ANA SHARYD</t>
-  </si>
-  <si>
-    <t>RAMIREZ CASTILLO</t>
-  </si>
-  <si>
-    <t>KnX714i</t>
-  </si>
-  <si>
-    <t>WILMER MATEO</t>
-  </si>
-  <si>
-    <t>CALDERON PALOMO</t>
-  </si>
-  <si>
-    <t>WNZ37rb</t>
-  </si>
-  <si>
-    <t>VERONICA</t>
-  </si>
-  <si>
-    <t>VANEGAS VASQUEZ</t>
-  </si>
-  <si>
-    <t>GrGLJUM</t>
-  </si>
-  <si>
-    <t>JUAN ESTEBAN</t>
-  </si>
-  <si>
-    <t>GARCIA CASTELLANOS</t>
-  </si>
-  <si>
-    <t>9HKmVtR</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MORENO ESCOBAR</t>
-  </si>
-  <si>
-    <t>DqQUdxq</t>
-  </si>
-  <si>
-    <t>ROJAS GUZMAN</t>
-  </si>
-  <si>
-    <t>JHmGvZC</t>
-  </si>
-  <si>
-    <t>KAHORY ALEJANDRA</t>
-  </si>
-  <si>
-    <t>VILLAR CASTAÑO</t>
-  </si>
-  <si>
-    <t>T8hKUJQ</t>
   </si>
 </sst>
 </file>
@@ -1260,7 +1269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -1285,7 +1294,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>102202026</v>
+        <v>111022026</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
@@ -1302,7 +1311,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>102232026</v>
+        <v>102092026</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -1314,29 +1323,29 @@
         <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>112042026</v>
+        <v>111072026</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>102132026</v>
+        <v>101022026</v>
       </c>
       <c r="C5" t="s">
         <v>17</v>
@@ -1348,233 +1357,233 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>112192026</v>
+        <v>101172026</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
         <v>20</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>101152026</v>
+        <v>112042026</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>112012026</v>
+        <v>101032026</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>112232026</v>
+        <v>102272026</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>101222026</v>
+        <v>101212026</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>112112026</v>
+        <v>102162026</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>101272026</v>
+        <v>111092026</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>102222026</v>
+        <v>112112026</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F13" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>112252026</v>
+        <v>111012026</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>101282026</v>
+        <v>102072026</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>102122026</v>
+        <v>102012026</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>101092026</v>
+        <v>101232026</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>111022026</v>
+        <v>102242026</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E18" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>111122026</v>
+        <v>111082026</v>
       </c>
       <c r="C19" t="s">
         <v>61</v>
@@ -1586,12 +1595,12 @@
         <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>111232026</v>
+        <v>112212026</v>
       </c>
       <c r="C20" t="s">
         <v>64</v>
@@ -1603,12 +1612,12 @@
         <v>66</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21">
-        <v>101142026</v>
+        <v>102222026</v>
       </c>
       <c r="C21" t="s">
         <v>67</v>
@@ -1620,12 +1629,12 @@
         <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22">
-        <v>112102026</v>
+        <v>111112026</v>
       </c>
       <c r="C22" t="s">
         <v>70</v>
@@ -1637,12 +1646,12 @@
         <v>72</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23">
-        <v>101192026</v>
+        <v>112142026</v>
       </c>
       <c r="C23" t="s">
         <v>73</v>
@@ -1654,12 +1663,12 @@
         <v>75</v>
       </c>
       <c r="F23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24">
-        <v>101112026</v>
+        <v>101042026</v>
       </c>
       <c r="C24" t="s">
         <v>76</v>
@@ -1671,12 +1680,12 @@
         <v>78</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25">
-        <v>111132026</v>
+        <v>101112026</v>
       </c>
       <c r="C25" t="s">
         <v>79</v>
@@ -1688,12 +1697,12 @@
         <v>81</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26">
-        <v>102182026</v>
+        <v>101122026</v>
       </c>
       <c r="C26" t="s">
         <v>82</v>
@@ -1705,12 +1714,12 @@
         <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27">
-        <v>101022026</v>
+        <v>101102026</v>
       </c>
       <c r="C27" t="s">
         <v>85</v>
@@ -1722,12 +1731,12 @@
         <v>87</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28">
-        <v>112082026</v>
+        <v>112192026</v>
       </c>
       <c r="C28" t="s">
         <v>88</v>
@@ -1739,12 +1748,12 @@
         <v>90</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29">
-        <v>102252026</v>
+        <v>102152026</v>
       </c>
       <c r="C29" t="s">
         <v>91</v>
@@ -1756,12 +1765,12 @@
         <v>93</v>
       </c>
       <c r="F29" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30">
-        <v>102112026</v>
+        <v>111172026</v>
       </c>
       <c r="C30" t="s">
         <v>94</v>
@@ -1778,7 +1787,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31">
-        <v>102072026</v>
+        <v>111182026</v>
       </c>
       <c r="C31" t="s">
         <v>97</v>
@@ -1795,7 +1804,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32">
-        <v>111032026</v>
+        <v>101282026</v>
       </c>
       <c r="C32" t="s">
         <v>100</v>
@@ -1807,12 +1816,12 @@
         <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33">
-        <v>102092026</v>
+        <v>102022026</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
@@ -1824,117 +1833,117 @@
         <v>105</v>
       </c>
       <c r="F33" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34">
-        <v>111182026</v>
+        <v>112152026</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="D34" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E34" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F34" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35">
-        <v>111152026</v>
+        <v>101192026</v>
       </c>
       <c r="C35" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36">
-        <v>111212026</v>
+        <v>102112026</v>
       </c>
       <c r="C36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D36" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37">
-        <v>112152026</v>
+        <v>102132026</v>
       </c>
       <c r="C37" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E37" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F37" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38">
-        <v>112162026</v>
+        <v>101252026</v>
       </c>
       <c r="C38" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F38" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39">
-        <v>112242026</v>
+        <v>112172026</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E39" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40">
-        <v>112022026</v>
+        <v>112062026</v>
       </c>
       <c r="C40" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
         <v>124</v>
@@ -1943,12 +1952,12 @@
         <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41">
-        <v>101072026</v>
+        <v>102192026</v>
       </c>
       <c r="C41" t="s">
         <v>126</v>
@@ -1960,12 +1969,12 @@
         <v>128</v>
       </c>
       <c r="F41" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42">
-        <v>112052026</v>
+        <v>101262026</v>
       </c>
       <c r="C42" t="s">
         <v>129</v>
@@ -1977,12 +1986,12 @@
         <v>131</v>
       </c>
       <c r="F42" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43">
-        <v>111012026</v>
+        <v>112232026</v>
       </c>
       <c r="C43" t="s">
         <v>132</v>
@@ -1994,12 +2003,12 @@
         <v>134</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44">
-        <v>112122026</v>
+        <v>102202026</v>
       </c>
       <c r="C44" t="s">
         <v>135</v>
@@ -2011,12 +2020,12 @@
         <v>137</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45">
-        <v>101102026</v>
+        <v>101272026</v>
       </c>
       <c r="C45" t="s">
         <v>138</v>
@@ -2028,12 +2037,12 @@
         <v>140</v>
       </c>
       <c r="F45" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46">
-        <v>101172026</v>
+        <v>112162026</v>
       </c>
       <c r="C46" t="s">
         <v>141</v>
@@ -2045,12 +2054,12 @@
         <v>143</v>
       </c>
       <c r="F46" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47">
-        <v>112172026</v>
+        <v>111142026</v>
       </c>
       <c r="C47" t="s">
         <v>144</v>
@@ -2062,12 +2071,12 @@
         <v>146</v>
       </c>
       <c r="F47" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48">
-        <v>102032026</v>
+        <v>102062026</v>
       </c>
       <c r="C48" t="s">
         <v>147</v>
@@ -2079,12 +2088,12 @@
         <v>149</v>
       </c>
       <c r="F48" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49">
-        <v>112092026</v>
+        <v>102102026</v>
       </c>
       <c r="C49" t="s">
         <v>150</v>
@@ -2096,117 +2105,117 @@
         <v>152</v>
       </c>
       <c r="F49" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50">
-        <v>101032026</v>
+        <v>102262026</v>
       </c>
       <c r="C50" t="s">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="D50" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E50" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F50" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51">
-        <v>111222026</v>
+        <v>102122026</v>
       </c>
       <c r="C51" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D51" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E51" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52">
-        <v>112062026</v>
+        <v>101092026</v>
       </c>
       <c r="C52" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D52" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E52" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:6">
       <c r="A53">
-        <v>112032026</v>
+        <v>111052026</v>
       </c>
       <c r="C53" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E53" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F53" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:6">
       <c r="A54">
-        <v>102102026</v>
+        <v>101142026</v>
       </c>
       <c r="C54" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D54" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E54" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F54" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:6">
       <c r="A55">
-        <v>101082026</v>
+        <v>111212026</v>
       </c>
       <c r="C55" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E55" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F55" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:6">
       <c r="A56">
-        <v>101252026</v>
+        <v>111062026</v>
       </c>
       <c r="C56" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="D56" t="s">
         <v>170</v>
@@ -2215,12 +2224,12 @@
         <v>171</v>
       </c>
       <c r="F56" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:6">
       <c r="A57">
-        <v>101062026</v>
+        <v>111102026</v>
       </c>
       <c r="C57" t="s">
         <v>172</v>
@@ -2232,49 +2241,49 @@
         <v>174</v>
       </c>
       <c r="F57" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:6">
       <c r="A58">
-        <v>111042026</v>
+        <v>111162026</v>
       </c>
       <c r="C58" t="s">
-        <v>33</v>
+        <v>175</v>
       </c>
       <c r="D58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E58" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:6">
       <c r="A59">
-        <v>111112026</v>
+        <v>111242026</v>
       </c>
       <c r="C59" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D59" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E59" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F59" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6">
       <c r="A60">
-        <v>102242026</v>
+        <v>102182026</v>
       </c>
       <c r="C60" t="s">
-        <v>180</v>
+        <v>97</v>
       </c>
       <c r="D60" t="s">
         <v>181</v>
@@ -2283,12 +2292,12 @@
         <v>182</v>
       </c>
       <c r="F60" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:6">
       <c r="A61">
-        <v>102192026</v>
+        <v>111192026</v>
       </c>
       <c r="C61" t="s">
         <v>183</v>
@@ -2305,7 +2314,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62">
-        <v>111142026</v>
+        <v>111032026</v>
       </c>
       <c r="C62" t="s">
         <v>186</v>
@@ -2317,55 +2326,55 @@
         <v>188</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6">
       <c r="A63">
-        <v>111072026</v>
+        <v>111122026</v>
       </c>
       <c r="C63" t="s">
+        <v>175</v>
+      </c>
+      <c r="D63" t="s">
         <v>189</v>
       </c>
-      <c r="D63" t="s">
+      <c r="E63" t="s">
         <v>190</v>
       </c>
-      <c r="E63" t="s">
-        <v>191</v>
-      </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64">
-        <v>101042026</v>
+        <v>101162026</v>
       </c>
       <c r="C64" t="s">
+        <v>191</v>
+      </c>
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="s">
         <v>192</v>
       </c>
-      <c r="D64" t="s">
-        <v>193</v>
-      </c>
-      <c r="E64" t="s">
-        <v>194</v>
-      </c>
       <c r="F64" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:6">
       <c r="A65">
-        <v>102262026</v>
+        <v>111152026</v>
       </c>
       <c r="C65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D65" t="s">
+        <v>194</v>
+      </c>
+      <c r="E65" t="s">
         <v>195</v>
-      </c>
-      <c r="D65" t="s">
-        <v>196</v>
-      </c>
-      <c r="E65" t="s">
-        <v>197</v>
       </c>
       <c r="F65" t="s">
         <v>9</v>
@@ -2373,78 +2382,78 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66">
-        <v>112222026</v>
+        <v>102212026</v>
       </c>
       <c r="C66" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="D66" t="s">
+        <v>197</v>
+      </c>
+      <c r="E66" t="s">
         <v>198</v>
       </c>
-      <c r="E66" t="s">
-        <v>199</v>
-      </c>
       <c r="F66" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:6">
       <c r="A67">
-        <v>112202026</v>
+        <v>112252026</v>
       </c>
       <c r="C67" t="s">
+        <v>199</v>
+      </c>
+      <c r="D67" t="s">
         <v>200</v>
       </c>
-      <c r="D67" t="s">
+      <c r="E67" t="s">
         <v>201</v>
       </c>
-      <c r="E67" t="s">
-        <v>202</v>
-      </c>
       <c r="F67" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" spans="1:6">
       <c r="A68">
-        <v>111082026</v>
+        <v>112102026</v>
       </c>
       <c r="C68" t="s">
+        <v>202</v>
+      </c>
+      <c r="D68" t="s">
         <v>203</v>
       </c>
-      <c r="D68" t="s">
+      <c r="E68" t="s">
         <v>204</v>
       </c>
-      <c r="E68" t="s">
-        <v>205</v>
-      </c>
       <c r="F68" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:6">
       <c r="A69">
-        <v>112142026</v>
+        <v>112012026</v>
       </c>
       <c r="C69" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69" t="s">
         <v>206</v>
       </c>
-      <c r="D69" t="s">
+      <c r="E69" t="s">
         <v>207</v>
       </c>
-      <c r="E69" t="s">
-        <v>208</v>
-      </c>
       <c r="F69" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:6">
       <c r="A70">
-        <v>111162026</v>
+        <v>102032026</v>
       </c>
       <c r="C70" t="s">
-        <v>61</v>
+        <v>208</v>
       </c>
       <c r="D70" t="s">
         <v>209</v>
@@ -2453,12 +2462,12 @@
         <v>210</v>
       </c>
       <c r="F70" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:6">
       <c r="A71">
-        <v>101132026</v>
+        <v>101202026</v>
       </c>
       <c r="C71" t="s">
         <v>211</v>
@@ -2470,12 +2479,12 @@
         <v>213</v>
       </c>
       <c r="F71" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:6">
       <c r="A72">
-        <v>101242026</v>
+        <v>112132026</v>
       </c>
       <c r="C72" t="s">
         <v>214</v>
@@ -2487,38 +2496,38 @@
         <v>216</v>
       </c>
       <c r="F72" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73" spans="1:6">
       <c r="A73">
-        <v>111242026</v>
+        <v>111132026</v>
       </c>
       <c r="C73" t="s">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="D73" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E73" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:6">
       <c r="A74">
-        <v>102082026</v>
+        <v>111042026</v>
       </c>
       <c r="C74" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D74" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E74" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F74" t="s">
         <v>9</v>
@@ -2526,78 +2535,78 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75">
-        <v>112132026</v>
+        <v>112202026</v>
       </c>
       <c r="C75" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D75" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E75" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F75" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76">
-        <v>102212026</v>
+        <v>112182026</v>
       </c>
       <c r="C76" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E76" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F76" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77">
-        <v>102162026</v>
+        <v>101242026</v>
       </c>
       <c r="C77" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D77" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E77" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F77" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:6">
       <c r="A78">
-        <v>111172026</v>
+        <v>102232026</v>
       </c>
       <c r="C78" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E78" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F78" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:6">
       <c r="A79">
-        <v>101202026</v>
+        <v>112052026</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="D79" t="s">
         <v>235</v>
@@ -2606,12 +2615,12 @@
         <v>236</v>
       </c>
       <c r="F79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:6">
       <c r="A80">
-        <v>102172026</v>
+        <v>101152026</v>
       </c>
       <c r="C80" t="s">
         <v>237</v>
@@ -2623,15 +2632,15 @@
         <v>239</v>
       </c>
       <c r="F80" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:6">
       <c r="A81">
-        <v>101122026</v>
+        <v>101222026</v>
       </c>
       <c r="C81" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="D81" t="s">
         <v>240</v>
@@ -2640,38 +2649,38 @@
         <v>241</v>
       </c>
       <c r="F81" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:6">
       <c r="A82">
-        <v>102042026</v>
+        <v>101182026</v>
       </c>
       <c r="C82" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" t="s">
         <v>242</v>
       </c>
-      <c r="D82" t="s">
+      <c r="E82" t="s">
         <v>243</v>
       </c>
-      <c r="E82" t="s">
-        <v>244</v>
-      </c>
       <c r="F82" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:6">
       <c r="A83">
-        <v>102152026</v>
+        <v>111222026</v>
       </c>
       <c r="C83" t="s">
+        <v>244</v>
+      </c>
+      <c r="D83" t="s">
         <v>245</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E83" t="s">
         <v>246</v>
-      </c>
-      <c r="E83" t="s">
-        <v>247</v>
       </c>
       <c r="F83" t="s">
         <v>9</v>
@@ -2679,27 +2688,27 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84">
-        <v>102062026</v>
+        <v>112092026</v>
       </c>
       <c r="C84" t="s">
+        <v>247</v>
+      </c>
+      <c r="D84" t="s">
         <v>248</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>249</v>
       </c>
-      <c r="E84" t="s">
-        <v>250</v>
-      </c>
       <c r="F84" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="1:6">
       <c r="A85">
-        <v>102052026</v>
+        <v>112032026</v>
       </c>
       <c r="C85" t="s">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="D85" t="s">
         <v>251</v>
@@ -2708,12 +2717,12 @@
         <v>252</v>
       </c>
       <c r="F85" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86" spans="1:6">
       <c r="A86">
-        <v>101012026</v>
+        <v>101062026</v>
       </c>
       <c r="C86" t="s">
         <v>253</v>
@@ -2725,49 +2734,49 @@
         <v>255</v>
       </c>
       <c r="F86" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="A87">
-        <v>101162026</v>
+        <v>112242026</v>
       </c>
       <c r="C87" t="s">
         <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>142</v>
+        <v>257</v>
       </c>
       <c r="E87" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F87" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="1:6">
       <c r="A88">
-        <v>102012026</v>
+        <v>102082026</v>
       </c>
       <c r="C88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E88" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F88" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:6">
       <c r="A89">
-        <v>102022026</v>
+        <v>101072026</v>
       </c>
       <c r="C89" t="s">
-        <v>261</v>
+        <v>34</v>
       </c>
       <c r="D89" t="s">
         <v>262</v>
@@ -2776,12 +2785,12 @@
         <v>263</v>
       </c>
       <c r="F89" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6">
       <c r="A90">
-        <v>111092026</v>
+        <v>112082026</v>
       </c>
       <c r="C90" t="s">
         <v>264</v>
@@ -2793,15 +2802,15 @@
         <v>266</v>
       </c>
       <c r="F90" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:6">
       <c r="A91">
-        <v>111062026</v>
+        <v>112222026</v>
       </c>
       <c r="C91" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="D91" t="s">
         <v>267</v>
@@ -2810,100 +2819,100 @@
         <v>268</v>
       </c>
       <c r="F91" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:6">
       <c r="A92">
-        <v>111202026</v>
+        <v>102052026</v>
       </c>
       <c r="C92" t="s">
+        <v>97</v>
+      </c>
+      <c r="D92" t="s">
         <v>269</v>
       </c>
-      <c r="D92" t="s">
+      <c r="E92" t="s">
         <v>270</v>
       </c>
-      <c r="E92" t="s">
-        <v>271</v>
-      </c>
       <c r="F92" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:6">
       <c r="A93">
-        <v>112072026</v>
+        <v>112022026</v>
       </c>
       <c r="C93" t="s">
+        <v>271</v>
+      </c>
+      <c r="D93" t="s">
         <v>272</v>
       </c>
-      <c r="D93" t="s">
+      <c r="E93" t="s">
         <v>273</v>
       </c>
-      <c r="E93" t="s">
-        <v>274</v>
-      </c>
       <c r="F93" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:6">
       <c r="A94">
-        <v>101182026</v>
+        <v>101052026</v>
       </c>
       <c r="C94" t="s">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="D94" t="s">
+        <v>274</v>
+      </c>
+      <c r="E94" t="s">
         <v>275</v>
       </c>
-      <c r="E94" t="s">
-        <v>276</v>
-      </c>
       <c r="F94" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="95" spans="1:6">
       <c r="A95">
-        <v>102142026</v>
+        <v>102172026</v>
       </c>
       <c r="C95" t="s">
+        <v>276</v>
+      </c>
+      <c r="D95" t="s">
         <v>277</v>
       </c>
-      <c r="D95" t="s">
+      <c r="E95" t="s">
         <v>278</v>
       </c>
-      <c r="E95" t="s">
-        <v>279</v>
-      </c>
       <c r="F95" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:6">
       <c r="A96">
-        <v>112212026</v>
+        <v>111232026</v>
       </c>
       <c r="C96" t="s">
+        <v>279</v>
+      </c>
+      <c r="D96" t="s">
         <v>280</v>
       </c>
-      <c r="D96" t="s">
+      <c r="E96" t="s">
         <v>281</v>
       </c>
-      <c r="E96" t="s">
-        <v>282</v>
-      </c>
       <c r="F96" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97">
-        <v>101052026</v>
+        <v>101012026</v>
       </c>
       <c r="C97" t="s">
-        <v>54</v>
+        <v>282</v>
       </c>
       <c r="D97" t="s">
         <v>283</v>
@@ -2912,12 +2921,12 @@
         <v>284</v>
       </c>
       <c r="F97" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98" spans="1:6">
       <c r="A98">
-        <v>111192026</v>
+        <v>101082026</v>
       </c>
       <c r="C98" t="s">
         <v>285</v>
@@ -2929,12 +2938,12 @@
         <v>287</v>
       </c>
       <c r="F98" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:6">
       <c r="A99">
-        <v>111052026</v>
+        <v>111202026</v>
       </c>
       <c r="C99" t="s">
         <v>288</v>
@@ -2946,12 +2955,12 @@
         <v>290</v>
       </c>
       <c r="F99" t="s">
-        <v>60</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:6">
       <c r="A100">
-        <v>101232026</v>
+        <v>102252026</v>
       </c>
       <c r="C100" t="s">
         <v>291</v>
@@ -2963,12 +2972,12 @@
         <v>293</v>
       </c>
       <c r="F100" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:6">
       <c r="A101">
-        <v>111102026</v>
+        <v>112072026</v>
       </c>
       <c r="C101" t="s">
         <v>294</v>
@@ -2980,12 +2989,12 @@
         <v>296</v>
       </c>
       <c r="F101" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102" spans="1:6">
       <c r="A102">
-        <v>112182026</v>
+        <v>102142026</v>
       </c>
       <c r="C102" t="s">
         <v>297</v>
@@ -2997,32 +3006,32 @@
         <v>299</v>
       </c>
       <c r="F102" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:6">
       <c r="A103">
-        <v>101212026</v>
+        <v>112122026</v>
       </c>
       <c r="C103" t="s">
-        <v>126</v>
+        <v>300</v>
       </c>
       <c r="D103" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E103" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F103" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104" spans="1:6">
       <c r="A104">
-        <v>101262026</v>
+        <v>101132026</v>
       </c>
       <c r="C104" t="s">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="D104" t="s">
         <v>303</v>
@@ -3031,7 +3040,24 @@
         <v>304</v>
       </c>
       <c r="F104" t="s">
-        <v>26</v>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
+      <c r="A105">
+        <v>102042026</v>
+      </c>
+      <c r="C105" t="s">
+        <v>305</v>
+      </c>
+      <c r="D105" t="s">
+        <v>306</v>
+      </c>
+      <c r="E105" t="s">
+        <v>307</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
